--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
@@ -4,35 +4,41 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>券商</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金账户</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产代码</t>
+  </si>
+  <si>
+    <t>资产名称</t>
   </si>
   <si>
     <t>标准券再折算率（%）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始使用日期</t>
+  </si>
+  <si>
+    <t>结束使用日期</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,12 +52,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -383,13 +383,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,6 +400,15 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>券商</t>
   </si>
@@ -32,6 +32,10 @@
   </si>
   <si>
     <t>结束使用日期</t>
+  </si>
+  <si>
+    <t>资金账户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -383,31 +387,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="1" max="2" width="20.6328125" customWidth="1"/>
+    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001.xlsx
@@ -391,6 +391,7 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.6328125" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" customWidth="1"/>
     <col min="4" max="4" width="20.26953125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
